--- a/CardGameInterface.xlsx
+++ b/CardGameInterface.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Benjamin Ellinger\Desktop\Digipen\DES315\Grading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gary Yang\Documents\Programing\Unity\CardStuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB39F55-D930-4BA2-B15B-C4DCE9A0A73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFD21E6-D4B8-4818-886C-87370FC70073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66015" yWindow="2685" windowWidth="20385" windowHeight="13230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="22" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>POST-MORTEM (200+ Words)</t>
   </si>
@@ -1211,6 +1211,12 @@
       </rPr>
       <t xml:space="preserve"> if well-crafted with sophisticated animations when going both in and out.</t>
     </r>
+  </si>
+  <si>
+    <t>Full Credit</t>
+  </si>
+  <si>
+    <t>Partial Credit</t>
   </si>
 </sst>
 </file>
@@ -1671,60 +1677,32 @@
   </cellStyles>
   <dxfs count="72">
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -1740,40 +1718,54 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1790,7 +1782,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1800,14 +1813,35 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1824,6 +1858,48 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9"/>
         </patternFill>
       </fill>
@@ -1832,34 +1908,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1869,41 +1917,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9"/>
         </patternFill>
       </fill>
@@ -1921,7 +1934,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
+          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1945,13 +1958,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
@@ -2045,7 +2051,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2091,6 +2104,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
       </font>
@@ -2110,13 +2130,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
@@ -2131,7 +2144,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2141,28 +2168,14 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2172,7 +2185,21 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2186,21 +2213,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2208,13 +2221,6 @@
       <font>
         <strike val="0"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
@@ -2518,7 +2524,7 @@
     <row r="1" spans="1:5" s="3" customFormat="1" ht="23.4" thickBot="1">
       <c r="A1" s="18">
         <f>MIN(1,(MAX(D1,(SUM(A4:A963)+IF(ISBLANK(A2),0,MIN(0,A2-0.7))))))</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>8</v>
@@ -2528,7 +2534,7 @@
       </c>
       <c r="D1" s="33">
         <f>MAX(A6,0)+MAX(A11,0)+MAX(A16,0)+MAX(A21,0)+MAX(A26,0)+MAX(A31,0)+COUNTIF(A7:A9,"&gt;0")*0.01+COUNTIF(A12:A14,"&gt;0")*0.01+COUNTIF(A17:A19,"&gt;0")*0.01+COUNTIF(A22:A24,"&gt;0")*0.01+COUNTIF(A27:A28,"&gt;0")*0.01+COUNTIF(A32:A34,"&gt;0")*0.01</f>
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="E1" s="9"/>
     </row>
@@ -2574,33 +2580,39 @@
       <c r="E6" s="11"/>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A7" s="34" t="str">
+      <c r="A7" s="34">
         <f>IF(LEFT(B7,2)="No",-0.1,IF(LEFT(B7,7)="Partial",0.01,IF(LEFT(B7,4)="Full",0.03,IF(LEFT(B7,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B7" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C7" s="37" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A8" s="34" t="str">
+      <c r="A8" s="34">
         <f>IF(LEFT(B8,2)="No",-0.1,IF(LEFT(B8,7)="Partial",0.01,IF(LEFT(B8,4)="Full",0.03,IF(LEFT(B8,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B8" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C8" s="37" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="12"/>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A9" s="34" t="str">
+      <c r="A9" s="34">
         <f>IF(LEFT(B9,2)="No",-0.1,IF(LEFT(B9,7)="Partial",0.01,IF(LEFT(B9,4)="Full",0.03,IF(LEFT(B9,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B9" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C9" s="37" t="s">
         <v>20</v>
       </c>
@@ -2621,33 +2633,39 @@
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" ht="31.9" customHeight="1" thickBot="1">
-      <c r="A12" s="34" t="str">
+      <c r="A12" s="34">
         <f>IF(LEFT(B12,2)="No",-0.1,IF(LEFT(B12,7)="Partial",0.01,IF(LEFT(B12,4)="Full",0.03,IF(LEFT(B12,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B12" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C12" s="37" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="12"/>
     </row>
     <row r="13" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A13" s="34" t="str">
+      <c r="A13" s="34">
         <f>IF(LEFT(B13,2)="No",-0.1,IF(LEFT(B13,7)="Partial",0.01,IF(LEFT(B13,4)="Full",0.03,IF(LEFT(B13,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B13" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C13" s="37" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A14" s="34" t="str">
+      <c r="A14" s="34">
         <f>IF(LEFT(B14,2)="No",-0.1,IF(LEFT(B14,7)="Partial",0.01,IF(LEFT(B14,4)="Full",0.03,IF(LEFT(B14,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B14" s="35"/>
+        <v>0.01</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>39</v>
+      </c>
       <c r="C14" s="37" t="s">
         <v>23</v>
       </c>
@@ -2668,33 +2686,39 @@
       <c r="E16" s="12"/>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A17" s="34" t="str">
+      <c r="A17" s="34">
         <f>IF(LEFT(B17,2)="No",-0.1,IF(LEFT(B17,7)="Partial",0.01,IF(LEFT(B17,4)="Full",0.03,IF(LEFT(B17,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B17" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C17" s="37" t="s">
         <v>24</v>
       </c>
       <c r="E17" s="12"/>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="31.9" customHeight="1" thickBot="1">
-      <c r="A18" s="34" t="str">
+      <c r="A18" s="34">
         <f>IF(LEFT(B18,2)="No",-0.1,IF(LEFT(B18,7)="Partial",0.01,IF(LEFT(B18,4)="Full",0.03,IF(LEFT(B18,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B18" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C18" s="37" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="11"/>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A19" s="34" t="str">
+      <c r="A19" s="34">
         <f>IF(LEFT(B19,2)="No",-0.1,IF(LEFT(B19,7)="Partial",0.01,IF(LEFT(B19,4)="Full",0.03,IF(LEFT(B19,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B19" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C19" s="37" t="s">
         <v>28</v>
       </c>
@@ -2908,76 +2932,76 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B9">
-    <cfRule type="beginsWith" dxfId="70" priority="90" stopIfTrue="1" operator="beginsWith" text="Small">
+    <cfRule type="beginsWith" dxfId="70" priority="89" stopIfTrue="1" operator="beginsWith" text="No Progress">
+      <formula>LEFT(B6,LEN("No Progress"))="No Progress"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="69" priority="98" stopIfTrue="1" operator="beginsWith" text="Lots">
+      <formula>LEFT(B6,LEN("Lots"))="Lots"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="68" priority="94" stopIfTrue="1" operator="endsWith" text="Met">
+      <formula>RIGHT(B6,LEN("Met"))="Met"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="67" priority="93" stopIfTrue="1" operator="beginsWith" text="Big">
+      <formula>LEFT(B6,LEN("Big"))="Big"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="66" priority="92" stopIfTrue="1" operator="beginsWith" text="Full">
+      <formula>LEFT(B6,LEN("Full"))="Full"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="65" priority="91" stopIfTrue="1" operator="beginsWith" text="Some">
+      <formula>LEFT(B6,LEN("Some"))="Some"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="64" priority="90" stopIfTrue="1" operator="beginsWith" text="Small">
       <formula>LEFT(B6,LEN("Small"))="Small"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="69" priority="89" stopIfTrue="1" operator="beginsWith" text="No Progress">
-      <formula>LEFT(B6,LEN("No Progress"))="No Progress"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="68" priority="87" stopIfTrue="1" operator="endsWith" text="Missed">
+    <cfRule type="beginsWith" dxfId="63" priority="88" stopIfTrue="1" operator="beginsWith" text="Partial">
+      <formula>LEFT(B6,LEN("Partial"))="Partial"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="62" priority="87" stopIfTrue="1" operator="endsWith" text="Missed">
       <formula>RIGHT(B6,LEN("Missed"))="Missed"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="67" priority="86" stopIfTrue="1" operator="beginsWith" text="Not">
+    <cfRule type="beginsWith" dxfId="61" priority="86" stopIfTrue="1" operator="beginsWith" text="Not">
       <formula>LEFT(B6,LEN("Not"))="Not"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="66" priority="85" stopIfTrue="1" operator="beginsWith" text="No Credit">
+    <cfRule type="beginsWith" dxfId="60" priority="85" stopIfTrue="1" operator="beginsWith" text="No Credit">
       <formula>LEFT(B6,LEN("No Credit"))="No Credit"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="65" priority="98" stopIfTrue="1" operator="beginsWith" text="Lots">
-      <formula>LEFT(B6,LEN("Lots"))="Lots"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="64" priority="88" stopIfTrue="1" operator="beginsWith" text="Partial">
-      <formula>LEFT(B6,LEN("Partial"))="Partial"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="63" priority="94" stopIfTrue="1" operator="endsWith" text="Met">
-      <formula>RIGHT(B6,LEN("Met"))="Met"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="62" priority="93" stopIfTrue="1" operator="beginsWith" text="Big">
-      <formula>LEFT(B6,LEN("Big"))="Big"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="61" priority="92" stopIfTrue="1" operator="beginsWith" text="Full">
-      <formula>LEFT(B6,LEN("Full"))="Full"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="60" priority="91" stopIfTrue="1" operator="beginsWith" text="Some">
-      <formula>LEFT(B6,LEN("Some"))="Some"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:B14 B26:B29">
-    <cfRule type="beginsWith" dxfId="59" priority="84" stopIfTrue="1" operator="beginsWith" text="Lots">
+    <cfRule type="beginsWith" dxfId="59" priority="83" stopIfTrue="1" operator="beginsWith" text="Extra">
+      <formula>LEFT(B11,LEN("Extra"))="Extra"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="58" priority="82" stopIfTrue="1" operator="endsWith" text="Met">
+      <formula>RIGHT(B11,LEN("Met"))="Met"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="57" priority="81" stopIfTrue="1" operator="beginsWith" text="Big">
+      <formula>LEFT(B11,LEN("Big"))="Big"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="56" priority="79" stopIfTrue="1" operator="beginsWith" text="Some">
+      <formula>LEFT(B11,LEN("Some"))="Some"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="55" priority="78" stopIfTrue="1" operator="beginsWith" text="Small">
+      <formula>LEFT(B11,LEN("Small"))="Small"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="54" priority="77" stopIfTrue="1" operator="beginsWith" text="No Progress">
+      <formula>LEFT(B11,LEN("No Progress"))="No Progress"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="53" priority="76" stopIfTrue="1" operator="beginsWith" text="Partial">
+      <formula>LEFT(B11,LEN("Partial"))="Partial"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="52" priority="75" stopIfTrue="1" operator="endsWith" text="Missed">
+      <formula>RIGHT(B11,LEN("Missed"))="Missed"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="51" priority="74" stopIfTrue="1" operator="beginsWith" text="Not">
+      <formula>LEFT(B11,LEN("Not"))="Not"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="50" priority="73" stopIfTrue="1" operator="beginsWith" text="No Credit">
+      <formula>LEFT(B11,LEN("No Credit"))="No Credit"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="49" priority="80" stopIfTrue="1" operator="beginsWith" text="Full">
+      <formula>LEFT(B11,LEN("Full"))="Full"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="48" priority="84" stopIfTrue="1" operator="beginsWith" text="Lots">
       <formula>LEFT(B11,LEN("Lots"))="Lots"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="58" priority="83" stopIfTrue="1" operator="beginsWith" text="Extra">
-      <formula>LEFT(B11,LEN("Extra"))="Extra"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="57" priority="82" stopIfTrue="1" operator="endsWith" text="Met">
-      <formula>RIGHT(B11,LEN("Met"))="Met"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="56" priority="81" stopIfTrue="1" operator="beginsWith" text="Big">
-      <formula>LEFT(B11,LEN("Big"))="Big"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="55" priority="80" stopIfTrue="1" operator="beginsWith" text="Full">
-      <formula>LEFT(B11,LEN("Full"))="Full"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="54" priority="79" stopIfTrue="1" operator="beginsWith" text="Some">
-      <formula>LEFT(B11,LEN("Some"))="Some"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="53" priority="77" stopIfTrue="1" operator="beginsWith" text="No Progress">
-      <formula>LEFT(B11,LEN("No Progress"))="No Progress"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="52" priority="76" stopIfTrue="1" operator="beginsWith" text="Partial">
-      <formula>LEFT(B11,LEN("Partial"))="Partial"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="51" priority="75" stopIfTrue="1" operator="endsWith" text="Missed">
-      <formula>RIGHT(B11,LEN("Missed"))="Missed"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="50" priority="74" stopIfTrue="1" operator="beginsWith" text="Not">
-      <formula>LEFT(B11,LEN("Not"))="Not"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="49" priority="73" stopIfTrue="1" operator="beginsWith" text="No Credit">
-      <formula>LEFT(B11,LEN("No Credit"))="No Credit"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="48" priority="78" stopIfTrue="1" operator="beginsWith" text="Small">
-      <formula>LEFT(B11,LEN("Small"))="Small"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:B19">
@@ -3008,128 +3032,128 @@
     <cfRule type="beginsWith" dxfId="39" priority="9" stopIfTrue="1" operator="beginsWith" text="Big">
       <formula>LEFT(B16,LEN("Big"))="Big"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="38" priority="10" stopIfTrue="1" operator="endsWith" text="Met">
-      <formula>RIGHT(B16,LEN("Met"))="Met"</formula>
+    <cfRule type="beginsWith" dxfId="38" priority="11" stopIfTrue="1" operator="beginsWith" text="Extra">
+      <formula>LEFT(B16,LEN("Extra"))="Extra"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="37" priority="12" stopIfTrue="1" operator="beginsWith" text="Lots">
       <formula>LEFT(B16,LEN("Lots"))="Lots"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="36" priority="11" stopIfTrue="1" operator="beginsWith" text="Extra">
-      <formula>LEFT(B16,LEN("Extra"))="Extra"</formula>
+    <cfRule type="endsWith" dxfId="36" priority="10" stopIfTrue="1" operator="endsWith" text="Met">
+      <formula>RIGHT(B16,LEN("Met"))="Met"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:B24">
-    <cfRule type="beginsWith" dxfId="35" priority="57" stopIfTrue="1" operator="beginsWith" text="Big">
-      <formula>LEFT(B21,LEN("Big"))="Big"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="34" priority="51" stopIfTrue="1" operator="endsWith" text="Missed">
+    <cfRule type="endsWith" dxfId="35" priority="51" stopIfTrue="1" operator="endsWith" text="Missed">
       <formula>RIGHT(B21,LEN("Missed"))="Missed"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="33" priority="52" stopIfTrue="1" operator="beginsWith" text="Partial">
+    <cfRule type="beginsWith" dxfId="34" priority="52" stopIfTrue="1" operator="beginsWith" text="Partial">
       <formula>LEFT(B21,LEN("Partial"))="Partial"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="32" priority="55" stopIfTrue="1" operator="beginsWith" text="Some">
+    <cfRule type="beginsWith" dxfId="33" priority="53" stopIfTrue="1" operator="beginsWith" text="No Progress">
+      <formula>LEFT(B21,LEN("No Progress"))="No Progress"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="32" priority="54" stopIfTrue="1" operator="beginsWith" text="Small">
+      <formula>LEFT(B21,LEN("Small"))="Small"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="31" priority="55" stopIfTrue="1" operator="beginsWith" text="Some">
       <formula>LEFT(B21,LEN("Some"))="Some"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="31" priority="54" stopIfTrue="1" operator="beginsWith" text="Small">
-      <formula>LEFT(B21,LEN("Small"))="Small"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="30" priority="56" stopIfTrue="1" operator="beginsWith" text="Full">
       <formula>LEFT(B21,LEN("Full"))="Full"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="29" priority="49" stopIfTrue="1" operator="beginsWith" text="No Credit">
-      <formula>LEFT(B21,LEN("No Credit"))="No Credit"</formula>
+    <cfRule type="beginsWith" dxfId="29" priority="57" stopIfTrue="1" operator="beginsWith" text="Big">
+      <formula>LEFT(B21,LEN("Big"))="Big"</formula>
     </cfRule>
     <cfRule type="endsWith" dxfId="28" priority="58" stopIfTrue="1" operator="endsWith" text="Met">
       <formula>RIGHT(B21,LEN("Met"))="Met"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="27" priority="59" stopIfTrue="1" operator="beginsWith" text="Extra">
-      <formula>LEFT(B21,LEN("Extra"))="Extra"</formula>
+    <cfRule type="beginsWith" dxfId="27" priority="50" stopIfTrue="1" operator="beginsWith" text="Not">
+      <formula>LEFT(B21,LEN("Not"))="Not"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="26" priority="60" stopIfTrue="1" operator="beginsWith" text="Lots">
       <formula>LEFT(B21,LEN("Lots"))="Lots"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="25" priority="53" stopIfTrue="1" operator="beginsWith" text="No Progress">
-      <formula>LEFT(B21,LEN("No Progress"))="No Progress"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="24" priority="50" stopIfTrue="1" operator="beginsWith" text="Not">
-      <formula>LEFT(B21,LEN("Not"))="Not"</formula>
+    <cfRule type="beginsWith" dxfId="25" priority="49" stopIfTrue="1" operator="beginsWith" text="No Credit">
+      <formula>LEFT(B21,LEN("No Credit"))="No Credit"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="24" priority="59" stopIfTrue="1" operator="beginsWith" text="Extra">
+      <formula>LEFT(B21,LEN("Extra"))="Extra"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:B34">
-    <cfRule type="beginsWith" dxfId="23" priority="25" stopIfTrue="1" operator="beginsWith" text="No Credit">
-      <formula>LEFT(B31,LEN("No Credit"))="No Credit"</formula>
+    <cfRule type="beginsWith" dxfId="23" priority="29" stopIfTrue="1" operator="beginsWith" text="No Progress">
+      <formula>LEFT(B31,LEN("No Progress"))="No Progress"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="22" priority="36" stopIfTrue="1" operator="beginsWith" text="Lots">
       <formula>LEFT(B31,LEN("Lots"))="Lots"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="21" priority="33" stopIfTrue="1" operator="beginsWith" text="Big">
+    <cfRule type="beginsWith" dxfId="21" priority="35" stopIfTrue="1" operator="beginsWith" text="Extra">
+      <formula>LEFT(B31,LEN("Extra"))="Extra"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="20" priority="34" stopIfTrue="1" operator="endsWith" text="Met">
+      <formula>RIGHT(B31,LEN("Met"))="Met"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="19" priority="33" stopIfTrue="1" operator="beginsWith" text="Big">
       <formula>LEFT(B31,LEN("Big"))="Big"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="20" priority="32" stopIfTrue="1" operator="beginsWith" text="Full">
+    <cfRule type="beginsWith" dxfId="18" priority="32" stopIfTrue="1" operator="beginsWith" text="Full">
       <formula>LEFT(B31,LEN("Full"))="Full"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="19" priority="31" stopIfTrue="1" operator="beginsWith" text="Some">
+    <cfRule type="beginsWith" dxfId="17" priority="31" stopIfTrue="1" operator="beginsWith" text="Some">
       <formula>LEFT(B31,LEN("Some"))="Some"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="18" priority="35" stopIfTrue="1" operator="beginsWith" text="Extra">
-      <formula>LEFT(B31,LEN("Extra"))="Extra"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="17" priority="30" stopIfTrue="1" operator="beginsWith" text="Small">
+    <cfRule type="beginsWith" dxfId="16" priority="30" stopIfTrue="1" operator="beginsWith" text="Small">
       <formula>LEFT(B31,LEN("Small"))="Small"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="16" priority="29" stopIfTrue="1" operator="beginsWith" text="No Progress">
-      <formula>LEFT(B31,LEN("No Progress"))="No Progress"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="15" priority="34" stopIfTrue="1" operator="endsWith" text="Met">
-      <formula>RIGHT(B31,LEN("Met"))="Met"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="14" priority="28" stopIfTrue="1" operator="beginsWith" text="Partial">
+    <cfRule type="endsWith" dxfId="15" priority="27" stopIfTrue="1" operator="endsWith" text="Missed">
+      <formula>RIGHT(B31,LEN("Missed"))="Missed"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="14" priority="26" stopIfTrue="1" operator="beginsWith" text="Not">
+      <formula>LEFT(B31,LEN("Not"))="Not"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="13" priority="25" stopIfTrue="1" operator="beginsWith" text="No Credit">
+      <formula>LEFT(B31,LEN("No Credit"))="No Credit"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="12" priority="28" stopIfTrue="1" operator="beginsWith" text="Partial">
       <formula>LEFT(B31,LEN("Partial"))="Partial"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="13" priority="27" stopIfTrue="1" operator="endsWith" text="Missed">
-      <formula>RIGHT(B31,LEN("Missed"))="Missed"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="12" priority="26" stopIfTrue="1" operator="beginsWith" text="Not">
-      <formula>LEFT(B31,LEN("Not"))="Not"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="beginsWith" dxfId="11" priority="14" stopIfTrue="1" operator="beginsWith" text="Not">
+    <cfRule type="beginsWith" dxfId="11" priority="24" stopIfTrue="1" operator="beginsWith" text="Lots">
+      <formula>LEFT(B36,LEN("Lots"))="Lots"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="10" priority="23" stopIfTrue="1" operator="beginsWith" text="Extra">
+      <formula>LEFT(B36,LEN("Extra"))="Extra"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="9" priority="22" stopIfTrue="1" operator="endsWith" text="Met">
+      <formula>RIGHT(B36,LEN("Met"))="Met"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="8" priority="21" stopIfTrue="1" operator="beginsWith" text="Big">
+      <formula>LEFT(B36,LEN("Big"))="Big"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="7" priority="20" stopIfTrue="1" operator="beginsWith" text="Full">
+      <formula>LEFT(B36,LEN("Full"))="Full"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="6" priority="19" stopIfTrue="1" operator="beginsWith" text="Some">
+      <formula>LEFT(B36,LEN("Some"))="Some"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="5" priority="18" stopIfTrue="1" operator="beginsWith" text="Small">
+      <formula>LEFT(B36,LEN("Small"))="Small"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="4" priority="17" stopIfTrue="1" operator="beginsWith" text="No Progress">
+      <formula>LEFT(B36,LEN("No Progress"))="No Progress"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="3" priority="16" stopIfTrue="1" operator="beginsWith" text="Partial">
+      <formula>LEFT(B36,LEN("Partial"))="Partial"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="2" priority="15" stopIfTrue="1" operator="endsWith" text="Missed">
+      <formula>RIGHT(B36,LEN("Missed"))="Missed"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="1" priority="14" stopIfTrue="1" operator="beginsWith" text="Not">
       <formula>LEFT(B36,LEN("Not"))="Not"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="10" priority="15" stopIfTrue="1" operator="endsWith" text="Missed">
-      <formula>RIGHT(B36,LEN("Missed"))="Missed"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="9" priority="16" stopIfTrue="1" operator="beginsWith" text="Partial">
-      <formula>LEFT(B36,LEN("Partial"))="Partial"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="8" priority="17" stopIfTrue="1" operator="beginsWith" text="No Progress">
-      <formula>LEFT(B36,LEN("No Progress"))="No Progress"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="7" priority="18" stopIfTrue="1" operator="beginsWith" text="Small">
-      <formula>LEFT(B36,LEN("Small"))="Small"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="6" priority="13" stopIfTrue="1" operator="beginsWith" text="No Credit">
+    <cfRule type="beginsWith" dxfId="0" priority="13" stopIfTrue="1" operator="beginsWith" text="No Credit">
       <formula>LEFT(B36,LEN("No Credit"))="No Credit"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="5" priority="24" stopIfTrue="1" operator="beginsWith" text="Lots">
-      <formula>LEFT(B36,LEN("Lots"))="Lots"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="4" priority="23" stopIfTrue="1" operator="beginsWith" text="Extra">
-      <formula>LEFT(B36,LEN("Extra"))="Extra"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="3" priority="22" stopIfTrue="1" operator="endsWith" text="Met">
-      <formula>RIGHT(B36,LEN("Met"))="Met"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="2" priority="21" stopIfTrue="1" operator="beginsWith" text="Big">
-      <formula>LEFT(B36,LEN("Big"))="Big"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="1" priority="20" stopIfTrue="1" operator="beginsWith" text="Full">
-      <formula>LEFT(B36,LEN("Full"))="Full"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="0" priority="19" stopIfTrue="1" operator="beginsWith" text="Some">
-      <formula>LEFT(B36,LEN("Some"))="Some"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">

--- a/CardGameInterface.xlsx
+++ b/CardGameInterface.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gary Yang\Documents\Programing\Unity\CardStuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFD21E6-D4B8-4818-886C-87370FC70073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FA55D5-292F-4620-9083-DF43A3D01B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="Code Report" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/CardGameInterface.xlsx
+++ b/CardGameInterface.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gary Yang\Documents\Programing\Unity\CardStuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FA55D5-292F-4620-9083-DF43A3D01B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEBD0CF-ABC4-4683-8789-551D21C13EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="Code Report" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
   <si>
     <t>POST-MORTEM (200+ Words)</t>
   </si>
@@ -1218,6 +1217,860 @@
   </si>
   <si>
     <t>Partial Credit</t>
+  </si>
+  <si>
+    <t>Small Thing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Play space is entirely configureable in editor, that is to say the entire thing is defined by an elipse you can move around, and it will also let you configure how many players you want and they will all be eqally spaced out always with the player at the bottom.  The pause menu is also controlled by a gizmo that allows you to drag where you want them to move to and fro from as part of a list. I thought it was quite neat and woud be good for UI stuff in the future had I had more scale UI stuff. </t>
+  </si>
+  <si>
+    <t>Lab E Goals Met</t>
+  </si>
+  <si>
+    <t>// ( "Action List" ) 
+//===| Action Manager |============================================================
+public class ActionManager : MonoBehaviour
+{
+    private Queue&lt;ActionBase&gt; actionQueue = new Queue&lt;ActionBase&gt;();
+    private List&lt;ActionBase&gt; activeActions = new List&lt;ActionBase&gt;();
+    private bool islistBlocked = false;
+    public float globalTimeScale = 1f;
+    [SerializeField] private TextMeshProUGUI debugText; // Debug text for showing active actions  
+    [SerializeField] private bool debugMode = false;
+    void ToggleDebugText()
+    {
+        debugMode = !debugMode;
+        if (debugText == null) Debug.LogError("Debug Text is not assigned in the inspector!");
+        else debugText.gameObject.SetActive(debugMode);
+    }
+   void Update()
+    {
+        if (debugMode)
+        {
+            debugText.text = $"Active Actions: {activeActions.Count}" + "\n";
+        }
+        // Process active actions
+        for (int i = activeActions.Count - 1; i &gt;= 0; i--) 
+        {
+            var action = activeActions[i];
+            if (debugMode) debugText.text += action.GetActionState() + "\n";
+            // Check if action should start (after delay)
+            if (action.UpdateDelay()) action.Update();
+            if (action.isComplete) 
+            {   
+                action.onComplete?.Invoke();                
+                activeActions.RemoveAt(i);
+                // Only unblock if this was a blocking action
+                if (action.isBlocking) islistBlocked = false;
+            }
+        }
+        // Add new actions if not blocked
+        // Keep adding actions until we hit a blocking one or empty the queue
+        while (!islistBlocked &amp;&amp; actionQueue.Count &gt; 0)
+        {
+            ActionBase action = actionQueue.Dequeue();
+            activeActions.Add(action);
+            action.SetManager(this);
+            action.Start();
+            // If we hit a blocking action, stop adding more until it completes
+            if (action.isBlocking) 
+            { 
+                islistBlocked = true;
+                break;
+            }
+        }
+    }
+    public void AddAction(ActionBase action)
+    {
+        action.SetManager(this);        // action looks at the manager for global time scale
+        actionQueue.Enqueue(action);
+    }
+} // end of ActionManager// ( "Action List" ) 
+//===| Action Manager |============================================================
+public class ActionManager : MonoBehaviour
+{
+    private Queue&lt;ActionBase&gt; actionQueue = new Queue&lt;ActionBase&gt;();
+    private List&lt;ActionBase&gt; activeActions = new List&lt;ActionBase&gt;();
+    private bool islistBlocked = false;
+    public float globalTimeScale = 1f;
+    [SerializeField] private TextMeshProUGUI debugText; // Debug text for showing active actions  
+    [SerializeField] private bool debugMode = false;
+    void ToggleDebugText()
+    {
+        debugMode = !debugMode;
+        if (debugText == null) Debug.LogError("Debug Text is not assigned in the inspector!");
+        else debugText.gameObject.SetActive(debugMode);
+    }
+   void Update()
+    {
+        if (debugMode)
+        {
+            debugText.text = $"Active Actions: {activeActions.Count}" + "\n";
+        }
+        // Process active actions
+        for (int i = activeActions.Count - 1; i &gt;= 0; i--) 
+        {
+            var action = activeActions[i];
+            if (debugMode) debugText.text += action.GetActionState() + "\n";
+            // Check if action should start (after delay)
+            if (action.UpdateDelay()) action.Update();
+            if (action.isComplete) 
+            {   
+                action.onComplete?.Invoke();                
+                activeActions.RemoveAt(i);
+                // Only unblock if this was a blocking action
+                if (action.isBlocking) islistBlocked = false;
+            }
+        }
+        // Add new actions if not blocked
+        // Keep adding actions until we hit a blocking one or empty the queue
+        while (!islistBlocked &amp;&amp; actionQueue.Count &gt; 0)
+        {
+            ActionBase action = actionQueue.Dequeue();
+            activeActions.Add(action);
+            action.SetManager(this);
+            action.Start();
+            // If we hit a blocking action, stop adding more until it completes
+            if (action.isBlocking) 
+            { 
+                islistBlocked = true;
+                break;
+            }
+        }
+    }
+    public void AddAction(ActionBase action)
+    {
+        action.SetManager(this);        // action looks at the manager for global time scale
+        actionQueue.Enqueue(action);
+    }
+} // end of ActionManager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action List  Itself </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Various Actions </t>
+  </si>
+  <si>
+    <t>/// &lt;summary&gt;
+/// Fades a GameObject in or out by lerping alpha.
+/// Supports CanvasGroup (UI panels), SpriteRenderer (cards/sprites), and UnityEngine.UI.Image.
+/// If the GameObject has none of these, an error is logged.
+/// &lt;/summary&gt;
+public class FadeAction : GameObjectAction
+{
+    private float targetAlpha;
+    private float startAlpha;
+    private EaseFunction easeFunction;
+    // Cached components — only one will be non-null
+    private CanvasGroup canvasGroup;
+    private SpriteRenderer spriteRenderer;
+    private UnityEngine.UI.Image image;
+    public FadeAction(GameObject entity,
+                      float targetAlpha,
+                      float duration,
+                      float delay = 0f,
+                      EaseFunction easeFunction = null,
+                      bool blocking = true)
+        : base(entity)
+    {
+        this.targetAlpha  = Mathf.Clamp01(targetAlpha);
+        this.duration     = duration;
+        this.delay        = delay;
+        this.isBlocking   = blocking;
+        this.easeFunction = easeFunction ?? Easing.Linear;
+        // Cache whichever component exists — search children too for nested UI (e.g. TMP buttons)
+        // Priority: CanvasGroup &gt; Image &gt; SpriteRenderer
+        canvasGroup    = entity.GetComponent&lt;CanvasGroup&gt;()    ?? entity.GetComponentInChildren&lt;CanvasGroup&gt;();
+        image          = entity.GetComponent&lt;UnityEngine.UI.Image&gt;() ?? entity.GetComponentInChildren&lt;UnityEngine.UI.Image&gt;();
+        spriteRenderer = entity.GetComponent&lt;SpriteRenderer&gt;() ?? entity.GetComponentInChildren&lt;SpriteRenderer&gt;();
+        if (canvasGroup == null &amp;&amp; image == null &amp;&amp; spriteRenderer == null)
+            Debug.LogError($"FadeAction: {entity.name} has no CanvasGroup, Image, or SpriteRenderer to fade (searched children too).");
+    }
+    public override void Start()
+    {
+        base.Start();
+        startAlpha = GetCurrentAlpha();
+        if (!isPartOfSimultaneous)
+            onComplete = () =&gt; SetAlpha(targetAlpha);
+    }
+    protected override void OnDelayComplete()
+    {
+        base.OnDelayComplete();
+        startAlpha = GetCurrentAlpha(); // re-capture in case something changed during delay
+    }
+    public override void Update()
+    {
+        base.Update();
+        if (!hasStarted) return;
+        float t = Mathf.Clamp01(elapsed / duration);
+        if (t &gt;= 1f)
+        {
+            SetAlpha(targetAlpha);
+            return;
+        }
+        SetAlpha(Mathf.LerpUnclamped(startAlpha, targetAlpha, easeFunction(t)));
+    }
+    private float GetCurrentAlpha()
+    {
+        if (canvasGroup    != null) return canvasGroup.alpha;
+        if (image          != null) return image.color.a;
+        if (spriteRenderer != null) return spriteRenderer.color.a;
+        return 1f;
+    }
+    private void SetAlpha(float alpha)
+    {
+        if (canvasGroup != null)
+        {
+            canvasGroup.alpha = alpha;
+            return;
+        }
+        if (image != null)
+        {
+            Color c = image.color;
+            c.a = alpha;
+            image.color = c;
+            return;
+        }
+        if (spriteRenderer != null)
+        {
+            Color c = spriteRenderer.color;
+            c.a = alpha;
+            spriteRenderer.color = c;
+        }
+    }
+} // end of FadeAction</t>
+  </si>
+  <si>
+    <t>public class SimultaneousTransformActions : GameObjectAction
+{
+    private List&lt;GameObjectAction&gt; actions = new List&lt;GameObjectAction&gt;();
+    // Track which properties we're actually transforming
+    private bool hasTranslateAction = false;
+    private bool hasRotateAction = false;
+    private bool hasScaleAction = false;
+    private Vector3 finalPosition;
+    private Quaternion finalRotation;
+    private Vector3 finalScale;
+    // Constructor
+    public SimultaneousTransformActions(GameObject target, float delay = 0f, bool blocking = true) 
+        : base(target)
+    {
+        this.delay = delay;
+        this.isBlocking = blocking;
+        this.duration = 0f;
+        // Initialize final values to prevent null reference
+        finalPosition = Vector3.zero;
+        finalRotation = Quaternion.identity;
+        finalScale = Vector3.one;
+    }
+    // Add an action to this simultaneous group
+    public void AddAction(GameObjectAction action)
+    {
+        if (action.GetTargetObject() != targetObject)
+        {
+            Debug.LogError("Cannot add action with different target object to SimultaneousTransformActions");
+            return;
+        }
+        action.SetSimultaneousFlag(true);
+        actions.Add(action);
+        // Update the duration based on this action
+        duration = Mathf.Max(duration, action.duration + action.delay);
+        // Store target values based on action type
+        if (action is TranslateAction translateAction)
+        {
+            finalPosition = translateAction.GetTargetPosition();
+            hasTranslateAction = true;
+            //Debug.Log($"Added TranslateAction to {targetObject.name}: Target={finalPosition}");
+        }
+        else if (action is RotateAction rotateAction)
+        {
+            // Store the target rotation
+            finalRotation = Quaternion.Euler(rotateAction.GetTargetRotation());
+            hasRotateAction = true;
+            //Debug.Log($"Added RotateAction to {targetObject.name}: Target={rotateAction.GetTargetRotation()}");
+        }
+        else if (action is ScaleAction scaleAction)
+        {
+            finalScale = scaleAction.GetTargetScale();
+            hasScaleAction = true;
+            //Debug.Log($"Added ScaleAction to {targetObject.name}: Target={finalScale}");
+        }
+    }
+    public override void Start()
+    {
+        base.Start();
+        // Capture current transform state
+        startPosition = transform.position;
+        startRotation = transform.rotation;
+        startScale = transform.localScale;
+        // For properties without explicit actions, use current values as final values
+        if (!hasTranslateAction) finalPosition = startPosition;
+        if (!hasRotateAction) finalRotation = startRotation;
+        if (!hasScaleAction) finalScale = startScale;
+        /*
+        // Debug info
+        Debug.Log($"SimultaneousTransformActions Start for {targetObject.name}:");
+        Debug.Log($"  Duration={duration}, Delay={delay}");
+        Debug.Log($"  hasTranslateAction={hasTranslateAction}, hasRotateAction={hasRotateAction}, hasScaleAction={hasScaleAction}");
+        Debug.Log($"  Start Position: {startPosition}, Final Position: {finalPosition}");
+        Debug.Log($"  Start Rotation: {startRotation.eulerAngles}, Final Rotation: {finalRotation.eulerAngles}");
+        Debug.Log($"  Start Scale: {startScale}, Final Scale: {finalScale}");
+        */
+    }
+    protected override void OnDelayComplete()
+    {
+        base.OnDelayComplete();
+        // Recapture transforms in case they changed during the delay
+        Vector3 oldStartPosition = startPosition;
+        Quaternion oldStartRotation = startRotation;
+        Vector3 oldStartScale = startScale;
+        startPosition = transform.position;
+        startRotation = transform.rotation;
+        startScale = transform.localScale;
+        // For properties without explicit actions, update final values to match new current values
+        if (!hasTranslateAction) finalPosition = startPosition;
+        if (!hasRotateAction) finalRotation = startRotation;
+        if (!hasScaleAction) finalScale = startScale;
+        /*
+        // Debug info for transform updates
+        Debug.Log($"SimultaneousTransformActions Delay Complete for {targetObject.name}:");
+        if (oldStartPosition != startPosition)
+            Debug.Log($"  Position changed during delay: {oldStartPosition} -&gt; {startPosition}");
+        if (oldStartRotation != startRotation)
+            Debug.Log($"  Rotation changed during delay: {oldStartRotation.eulerAngles} -&gt; {startRotation.eulerAngles}");
+        if (oldStartScale != startScale)
+            Debug.Log($"  Scale changed during delay: {oldStartScale} -&gt; {startScale}");
+        */
+    }
+    public override void Update()
+    {
+        base.Update(); // Call base update for proper timing
+        // Only update if we've passed the delay
+        if (!hasStarted) return;
+        // Calculate normalized progress (0-1)
+        float t = Mathf.Clamp01(elapsed / duration);
+        // Get easing functions for each transform property
+        EaseFunction translateEase = Easing.Linear;
+        EaseFunction rotateEase = Easing.Linear;
+        EaseFunction scaleEase = Easing.Linear;
+        // Find easing functions from added actions
+        foreach (var action in actions)
+        {
+            if (action is TranslateAction transAction)
+                translateEase = transAction.GetEaseFunction();
+            else if (action is RotateAction rotAction)
+                rotateEase = rotAction.GetEaseFunction();
+            else if (action is ScaleAction scaleAction)
+                scaleEase = scaleAction.GetEaseFunction();
+        }
+        // Apply transform changes ONLY for actions that were explicitly added
+        if (hasTranslateAction)
+        {
+            float translationT = translateEase(t);
+            transform.position = Vector3.LerpUnclamped(startPosition, finalPosition, translationT);
+        }
+        if (hasRotateAction)
+        {
+            float rotationT = rotateEase(t);
+            transform.rotation = Quaternion.SlerpUnclamped(startRotation, finalRotation, rotationT);
+        }
+        if (hasScaleAction)
+        {
+            float scaleT = scaleEase(t);
+            transform.localScale = Vector3.LerpUnclamped(startScale, finalScale, scaleT);
+        }
+        // Handle completion
+        if (isComplete)
+        {
+            // Ensure we end exactly at the target transforms, but ONLY for properties we're modifying
+            if (hasTranslateAction) transform.position = finalPosition;
+            if (hasRotateAction) transform.rotation = finalRotation;
+            if (hasScaleAction) transform.localScale = finalScale;
+            //Debug.Log($"SimultaneousTransformActions Complete for {targetObject.name}");
+        }
+    }
+} // end of SimultaneousTransformActions</t>
+  </si>
+  <si>
+    <t>public class FlipAction : RotateAction
+{
+    public FlipAction(GameObject entity, float duration, float delay = 0f, bool blocking = false) 
+        : base(entity, CalculateFlipTarget(entity), duration, delay, Easing.Linear, blocking) { }
+    private static Vector3 CalculateFlipTarget(GameObject entity)
+    {
+        // Get current rotation and add 180 to X axis for flip
+        Vector3 current = entity.transform.eulerAngles;
+        return new Vector3(current.x + 180f, current.y, current.z);
+    }
+}</t>
+  </si>
+  <si>
+    <t>/// &lt;summary&gt;
+/// Specify a target rotation for a game object
+/// NOTE: this is an absolute rotation, not a relative rotation this is the target rotation
+/// &lt;/summary&gt;
+public class RotateAction : GameObjectAction
+{
+    private Quaternion targetRotation;
+    private EaseFunction easeFunction;
+    private Vector3 targetEulerAngles;
+    public Vector3 GetTargetRotation() =&gt; targetEulerAngles;
+    public EaseFunction GetEaseFunction() =&gt; easeFunction;
+    public RotateAction( GameObject entity,
+                         Vector3 targetEulerAngles, 
+                         float duration, 
+                         float delay = 0f, 
+                         EaseFunction easeFunction = null, 
+                         bool blocking = true ) 
+        : base(entity)
+    {
+        this.targetEulerAngles = targetEulerAngles;     
+        this.targetRotation = Quaternion.Euler(targetEulerAngles);
+        this.duration = duration;
+        this.delay = delay;
+        this.isBlocking = blocking;
+        this.easeFunction = easeFunction ?? Easing.Linear;
+    }
+    public override void Start()
+    {
+        base.Start();
+        if (!isPartOfSimultaneous)
+        {
+            onComplete = () =&gt; targetObject.transform.rotation = targetRotation;
+        }
+    }
+    public override void Update()
+    {
+        base.Update(); // Call base update to handle elapsed time and completion
+        // Only update if we've passed the delay
+        if (!hasStarted) return;
+        // Use elapsed from base class - NOT incrementing here
+        float t = Mathf.Clamp01(elapsed / duration);
+        float easedT = easeFunction(t);
+        if (t &gt;= 1.0f)
+        {
+            targetObject.transform.rotation = targetRotation; // Ensure we reach exactly the target
+            return;
+        }
+        targetObject.transform.rotation = Quaternion.LerpUnclamped(startRotation, targetRotation, easedT);
+    }
+}</t>
+  </si>
+  <si>
+    <t>/// &lt;summary&gt;
+/// Translate a game object to a target position with optional easing, duration, and delay
+/// &lt;/summary&gt;
+public class TranslateAction : GameObjectAction
+{
+    private Vector3 targetPos;
+    private EaseFunction easeFunction;
+    public Vector3 GetTargetPosition() =&gt; targetPos;
+    public EaseFunction GetEaseFunction() =&gt; easeFunction;
+    // Constructor to create a TranslateAction
+    public TranslateAction(GameObject entity, Vector3 target, float duration, float delay = 0f, EaseFunction easeFunction = null, bool blocking = true) 
+        : base(entity)
+    {
+        this.targetPos = target;
+        this.duration = duration;
+        this.delay = delay;
+        this.isBlocking = blocking;
+        this.easeFunction = easeFunction ?? Easing.Linear;
+    }
+    public override void Start()
+    {
+        base.Start();
+        if (!isPartOfSimultaneous)
+        {
+            onComplete = () =&gt; targetObject.transform.position = targetPos;
+        }
+    }
+    public override void Update()
+    {
+        base.Update();
+        if (!hasStarted) return;
+        float t = Mathf.Clamp01(elapsed / duration);
+        float easedT = easeFunction(t);
+        if (t &gt;= 1.0f)
+        {
+            targetObject.transform.position = targetPos;
+            return;
+        }
+        // Use startPosition from the base class
+        targetObject.transform.position = Vector3.LerpUnclamped(startPosition, targetPos, easedT);
+    }
+    // protected override void OnDelayComplete()
+    // {
+    //     // Recapture start position when delay completes
+    //     // This ensures we start from current position after delay
+    //     startPos = targetObject.transform.position;
+    // }
+} // end of TranslateAction</t>
+  </si>
+  <si>
+    <t>public class ScaleAction : GameObjectAction
+{
+    private Vector3 targetScale;
+    private EaseFunction easeFunction;
+    public Vector3 GetTargetScale() =&gt; targetScale;
+    public EaseFunction GetEaseFunction() =&gt; easeFunction;
+    public ScaleAction( GameObject entity,
+                        Vector3 targetScale, 
+                        float duration, 
+                        float delay = 0f, 
+                        EaseFunction easeFunction = null,
+                        bool blocking = true ) 
+        : base(entity)
+    {
+        this.targetScale = targetScale;
+        this.duration = duration;
+        this.delay = delay;
+        this.isBlocking = blocking;
+        this.easeFunction = easeFunction ?? Easing.Linear;
+    }
+    public override void Start()
+    {
+        base.Start();
+        if (!isPartOfSimultaneous)
+        {
+            onComplete = () =&gt; targetObject.transform.localScale = targetScale;
+        }
+    }
+    public override void Update()
+    {
+        base.Update(); // Call base update to handle elapsed time and completion
+        // Only update if we've passed the delay
+        if (!hasStarted) return;
+        // Use elapsed from base class
+        float t = Mathf.Clamp01(elapsed / duration);
+        float easedT = easeFunction(t);
+        if (t &gt;= 1.0f)
+        {
+            targetObject.transform.localScale = targetScale; // Ensure we reach exactly the target
+            return;
+        }
+        // Use startScale from the base class
+        targetObject.transform.localScale = Vector3.LerpUnclamped(startScale, targetScale, easedT);
+    }
+} // end of ScaleAction</t>
+  </si>
+  <si>
+    <t>/// &lt;summary&gt;
+/// This action is to be used at the end of a sequence of actions to block the action list until the end of the sequence
+/// time should be probably set to or more than the duration of the sequence including delays
+/// &lt;/summary&gt;
+public class BlockAction : ActionBase
+{
+    public BlockAction(float duration)
+    {
+        this.duration = duration;
+        this.isBlocking = true;
+    }
+    public override void Update()
+    {
+        duration -= deltaTime;
+        isComplete = duration &lt;= 0f;
+    }
+}
+// Callback action to trigger a function when the action completes
+public class CallBackAction : ActionBase
+{
+    public CallBackAction(float duration, bool isBlocking, System.Action callback)
+    {
+        this.duration = duration;
+        this.onComplete = callback;
+        this.isBlocking = isBlocking;
+    }
+}
+//===| Game Object Level actions|=================================================
+// GameObject-level actions inherit from ActionBase, designed to act on a GameObject
+public abstract class GameObjectAction : ActionBase
+{
+    protected readonly GameObject targetObject;
+    protected readonly Transform transform;     // Cached for performance 
+    protected Vector3 startPosition;
+    protected Quaternion startRotation;
+    protected Vector3 startScale;
+    protected GameObjectAction(GameObject target)
+    {
+        this.targetObject = target;
+        this.transform = target.transform;
+    }
+    public GameObject GetTargetObject() =&gt; targetObject;
+    public override void Start()
+    {
+        base.Start();
+        // Cache the starting transform values
+        CaptureCurrentTransform();
+    }
+    protected void CaptureCurrentTransform()
+    {
+        startPosition = transform.position;
+        startRotation = transform.rotation;
+        startScale = transform.localScale;
+    }
+    // Override OnDelayComplete to recapture transform after delay
+    protected override void OnDelayComplete()
+    {
+        // Recapture all transforms when delay completes
+        CaptureCurrentTransform();
+    }
+}</t>
+  </si>
+  <si>
+    <t>public abstract class ActionBase
+{
+    public float duration; // total duration of the action
+    public float delay;    // delay before starting the action
+    public bool isBlocking;// if true, blocks subsequent actions until complete
+    public System.Action onComplete;
+    public bool isComplete;
+    public float timeScale = 1f;
+    protected ActionManager manager;             // Reference to manager for global timescale
+    protected bool isPartOfSimultaneous = false; // track if the action is part of a simultaneous action
+    protected bool hasStarted = false; // track if the action started or not 
+    protected float delayTimer = 0.0f; // delay timer 
+    protected float elapsed = 0.0f;    // track elapsed time separately from delay
+    protected float deltaTime =&gt; Time.deltaTime * timeScale * (manager != null ? manager.globalTimeScale : 1f);
+    public void SetManager(ActionManager manager)
+    {
+        this.manager = manager;
+    }
+    public void SetSimultaneousFlag(bool isSimultaneous)
+    {
+        this.isPartOfSimultaneous = isSimultaneous;
+    }
+    public virtual void Start() // IMPORTANT: for the delay to work properly inherited need to call base.Start() 
+    {                           //            if they override this class. 
+        delayTimer = 0f;
+        elapsed = 0f;
+        hasStarted = false;
+        isComplete = false; // Ensure we reset this when restarting
+    }
+    public virtual bool UpdateDelay()
+    {
+        if (hasStarted) return true; // delay is complete, return true
+        delayTimer += deltaTime;
+        if (delayTimer &gt;= delay)
+        {
+            hasStarted = true;
+            OnDelayComplete();
+            return true;
+        }
+        return false;
+    }
+    public virtual void Update()
+    {
+        if (hasStarted)
+        {
+            elapsed += deltaTime;
+            if (elapsed &gt;= duration)
+            {
+                isComplete = true;
+            }
+        }
+    }
+    protected virtual void OnDelayComplete() { }
+    public virtual string GetActionState()
+    {
+        return $"{GetType().Name} - Duration: {duration}, ElapsedTime: {deltaTime}, Delay: {delay}, " +
+               $"ElapsedDelay: {delayTimer} Blocking: {isBlocking} ";
+    }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pause menu </t>
+  </si>
+  <si>
+    <t>using System;
+using System.Collections;
+using System.Collections.Generic;
+using Unity.VisualScripting;
+using UnityEngine;
+using UnityEngine.UI;
+[System.Serializable] 
+public class GameObjectPair
+{
+    public GameObject objectToTransform;
+    public Vector3 targetPosition;       // where it animates TO (set via gizmo handle)
+    [HideInInspector] public Vector3 originalPosition; // cached at Start, set automatically
+}
+public class PauseMenuController : MonoBehaviour
+{
+    // This holds the objects that need to be toggled (droped down and fade in when the pause menu is activated, and then put back when the pause menu is deactivated)
+    [Header("Pair object with where it should animate to when the pause menu is activated")]
+    public List&lt;GameObjectPair&gt; _objectsToToggle = new List&lt;GameObjectPair&gt;();
+    public bool IsAnimating() { return _isAnimating; }
+    public bool IsActivated() { return _activated; }
+    [Header("Reference to the action manager to add the pause menu animations to")]
+    [SerializeField] public ActionManager _actionManager;
+    [DoNotSerialize] private bool _activated = false; 
+    [DoNotSerialize] private bool _isAnimating = false;
+    [Header("Sliders for size &amp; timescale options")] 
+    [SerializeField] private Slider _timeScaleSlider;
+    public float GetTimeScale() { return _timeScaleSlider.value; }
+    [SerializeField] private Slider _cardSizeSlider;
+    public float GetCardSize() { return _cardSizeSlider.value; }
+    // Start is called before the first frame update
+    void Start()
+    {
+        // Cache the original position of each object so we can return to it on deactivate
+        foreach (GameObjectPair pair in _objectsToToggle)
+        {
+            if (pair.objectToTransform != null)
+                pair.originalPosition = pair.objectToTransform.transform.position;
+        }
+    }
+    // Update is called once per frame
+    void Update()
+    {
+        if (_isAnimating) { return; } // if we're in the middle of an animation, ignore input to prevent spamming the pause menu
+        if (Input.GetKeyDown(KeyCode.Escape))
+        {
+            if (_activated) {
+                DeactivatePauseMenu();
+            } else {
+                ActivatePauseMenu();
+            }
+        }
+    }
+    private void ActivatePauseMenu()
+    {
+        _activated = true; 
+        _isAnimating = true;
+        const float animationDuration = 1.5f;
+        foreach (GameObjectPair pair in _objectsToToggle)
+        {
+            _actionManager.AddAction(new TranslateAction(
+                pair.objectToTransform,
+                pair.targetPosition,
+                animationDuration,
+                0.0f,
+                Easing.EaseInBounce,
+                false
+            ));
+            _actionManager.AddAction(new FadeAction(
+                pair.objectToTransform,
+                1.0f,
+                animationDuration,
+                0.0f,
+                Easing.EaseInCirc,
+                false
+            ));
+        }
+        _actionManager.AddAction(new CallBackAction(
+            animationDuration,
+            true,
+            () =&gt; { _isAnimating = false; }
+        ));
+    }
+    private void DeactivatePauseMenu()
+    {
+        _activated = false;
+        _isAnimating = true;
+        foreach (GameObjectPair pair in _objectsToToggle)
+        {
+            _actionManager.AddAction(new TranslateAction(
+                pair.objectToTransform,
+                pair.originalPosition,
+                1.5f,
+                0.0f,
+                Easing.EaseOutBounce,
+                false
+            ));
+            _actionManager.AddAction(new FadeAction(
+                pair.objectToTransform,
+                0.0f,
+                1.5f,
+                0.0f,
+                Easing.EaseInCirc,
+                false
+            ));
+        }
+        _actionManager.AddAction(new CallBackAction(
+            1.5f,
+            true,
+            () =&gt; { _isAnimating = false; }
+        ));
+    }
+    // Call this from a UI button to resume — same behaviour as pressing Escape while paused
+    public void Resume()
+    {
+        if (_isAnimating || !_activated) return;
+        DeactivatePauseMenu();
+    }
+#if UNITY_EDITOR
+    private void OnDrawGizmos()
+    {
+        if (_objectsToToggle == null) return;
+        foreach (GameObjectPair pair in _objectsToToggle)
+        {
+            if (pair.objectToTransform == null) continue;
+            Gizmos.color = Color.cyan;
+            Gizmos.DrawWireSphere(pair.targetPosition, 0.3f);
+            Gizmos.color = Color.yellow;
+            Gizmos.DrawLine(pair.objectToTransform.transform.position, pair.targetPosition);
+        }
+    }
+#endif
+}</t>
+  </si>
+  <si>
+    <t>using UnityEditor;
+using UnityEngine;
+[CustomEditor(typeof(PauseMenuController))]
+public class PauseMenuControllerEditor : Editor
+{
+    private void OnSceneGUI()
+    {
+        PauseMenuController controller = (PauseMenuController)target;
+        if (controller._objectsToToggle == null) return;
+        SerializedObject so = new SerializedObject(controller);
+        SerializedProperty listProp = so.FindProperty("_objectsToToggle");
+        for (int i = 0; i &lt; controller._objectsToToggle.Count; i++)
+        {
+            GameObjectPair pair = controller._objectsToToggle[i];
+            if (pair == null || pair.objectToTransform == null) continue;
+            Vector3 objPos = pair.objectToTransform.transform.position;
+            // If targetPosition hasn't been set yet, default it to the object's current position
+            SerializedProperty elementProp = listProp.GetArrayElementAtIndex(i);
+            SerializedProperty targetPosProp = elementProp.FindPropertyRelative("targetPosition");
+            if (targetPosProp.vector3Value == Vector3.zero)
+            {
+                so.Update();
+                targetPosProp.vector3Value = objPos;
+                so.ApplyModifiedPropertiesWithoutUndo();
+            }
+            Vector3 targetPos = pair.targetPosition;
+            // Draw the object's current/original position as a green wire sphere
+            Handles.color = Color.green;
+            Handles.DrawWireDisc(objPos, Vector3.forward, 0.3f);
+            Handles.Label(objPos + Vector3.up * 0.4f, $"{pair.objectToTransform.name} (start)", EditorStyles.miniLabel);
+            // Draw a line from object to target
+            Handles.color = Color.yellow;
+            Handles.DrawDottedLine(objPos, targetPos, 4f);
+            // Draw a draggable handle at the target position
+            Handles.color = Color.cyan;
+            EditorGUI.BeginChangeCheck();
+            Vector3 newPos = Handles.PositionHandle(targetPos, Quaternion.identity);
+            if (EditorGUI.EndChangeCheck())
+            {
+                Undo.RecordObject(controller, "Move Pause Target Position");
+                so.Update();
+                targetPosProp.vector3Value = newPos;
+                so.ApplyModifiedProperties();
+            }
+            Handles.Label(targetPos + Vector3.up * 0.4f, $"{pair.objectToTransform.name} (target)", EditorStyles.boldLabel);
+        }
+    }
+}</t>
+  </si>
+  <si>
+    <t>Oh many</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As with all projects I do in these des classes, nothing went to plan, everything broke last minuite, and everything could have been better. I've learned a lot about animation that I want to take into other applications. Doing this with Multiple channels seems to be exactly what they do in modern animation for human animations, just with a lot more quaternions and inverse kinematics / quaternion resolution. I’m seeing that this could be applied to that as a sequencer or have that be what happens under the hood with timed sequences etc. It could be applied to a lot of other applications as well. I’ve just barely scratched the surface of what I would like to do with this Command Pattern and I would LOVE to have time to edit this in the future when I’m not staring down the barrel of deadlines. But personal desires aside. The rotation system I had in place was objectively horrible, I should have had some overseer for card states, having rotations behave correctly while things are flipped up and down was an edge case nightmare and frankly had I known how children work. I should have kept the rotations done on the children instead of on the parrent structure because rotations screw with EVERYTHING. The number of whiteboards I could fill with me trying to figure out how to resolve all the cases I ran into (which I STILL haven’t fixed entirely) could fill up a library. But it works good enough, and the only bug left is that the last card of the round sometimes flips in weird directions when revealed and discarded. I also could have improved the actual game manager. I’ve never been good at architecting these and I should really consult a whiteboard next time instead of just writing till I run into problems. Because I have yet again, ended up with a giant oversized game manager rather than smaller piece-meal parts that I could individually modify. </t>
   </si>
 </sst>
 </file>
@@ -1528,7 +2381,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1670,6 +2523,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1680,21 +2536,35 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1704,6 +2574,13 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -1719,18 +2596,60 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9"/>
         </patternFill>
       </fill>
@@ -1739,34 +2658,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1776,28 +2667,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1814,42 +2684,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1866,6 +2701,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
@@ -1873,21 +2729,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1959,6 +2801,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
@@ -2059,6 +2915,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9"/>
         </patternFill>
       </fill>
@@ -2066,21 +2936,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2090,6 +2946,13 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -2105,18 +2968,53 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9"/>
         </patternFill>
       </fill>
@@ -2125,41 +3023,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2169,7 +3032,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2186,35 +3049,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2225,6 +3060,27 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2525,7 +3381,7 @@
     <row r="1" spans="1:5" s="3" customFormat="1" ht="23.4" thickBot="1">
       <c r="A1" s="18">
         <f>MIN(1,(MAX(D1,(SUM(A4:A963)+IF(ISBLANK(A2),0,MIN(0,A2-0.7))))))</f>
-        <v>0.25</v>
+        <v>0.42000000000000015</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>8</v>
@@ -2535,7 +3391,7 @@
       </c>
       <c r="D1" s="33">
         <f>MAX(A6,0)+MAX(A11,0)+MAX(A16,0)+MAX(A21,0)+MAX(A26,0)+MAX(A31,0)+COUNTIF(A7:A9,"&gt;0")*0.01+COUNTIF(A12:A14,"&gt;0")*0.01+COUNTIF(A17:A19,"&gt;0")*0.01+COUNTIF(A22:A24,"&gt;0")*0.01+COUNTIF(A27:A28,"&gt;0")*0.01+COUNTIF(A32:A34,"&gt;0")*0.01</f>
-        <v>0.09</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="E1" s="9"/>
     </row>
@@ -2740,33 +3596,39 @@
       <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A22" s="34" t="str">
+      <c r="A22" s="34">
         <f>IF(LEFT(B22,2)="No",-0.1,IF(LEFT(B22,7)="Partial",0.01,IF(LEFT(B22,4)="Full",0.03,IF(LEFT(B22,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B22" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C22" s="37" t="s">
         <v>37</v>
       </c>
       <c r="E22" s="40"/>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="31.9" customHeight="1" thickBot="1">
-      <c r="A23" s="34" t="str">
+      <c r="A23" s="34">
         <f>IF(LEFT(B23,2)="No",-0.1,IF(LEFT(B23,7)="Partial",0.01,IF(LEFT(B23,4)="Full",0.03,IF(LEFT(B23,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B23" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C23" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="12"/>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A24" s="34" t="str">
+      <c r="A24" s="34">
         <f>IF(LEFT(B24,2)="No",-0.1,IF(LEFT(B24,7)="Partial",0.01,IF(LEFT(B24,4)="Full",0.03,IF(LEFT(B24,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B24" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C24" s="37" t="s">
         <v>30</v>
       </c>
@@ -2787,33 +3649,39 @@
       <c r="E26" s="12"/>
     </row>
     <row r="27" spans="1:5" s="2" customFormat="1" ht="31.9" customHeight="1" thickBot="1">
-      <c r="A27" s="34" t="str">
+      <c r="A27" s="34">
         <f>IF(LEFT(B27,2)="No",-0.1,IF(LEFT(B27,7)="Partial",0.01,IF(LEFT(B27,4)="Full",0.03,IF(LEFT(B27,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B27" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C27" s="37" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="11"/>
     </row>
     <row r="28" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A28" s="34" t="str">
+      <c r="A28" s="34">
         <f>IF(LEFT(B28,2)="No",-0.1,IF(LEFT(B28,7)="Partial",0.01,IF(LEFT(B28,4)="Full",0.03,IF(LEFT(B28,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B28" s="35"/>
+        <v>0.03</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="C28" s="37" t="s">
         <v>34</v>
       </c>
       <c r="E28" s="12"/>
     </row>
     <row r="29" spans="1:5" s="2" customFormat="1" ht="31.5" thickBot="1">
-      <c r="A29" s="34" t="str">
+      <c r="A29" s="34">
         <f>IF(LEFT(B29,2)="No",-0.1,IF(LEFT(B29,7)="Partial",0.01,IF(LEFT(B29,4)="Full",0.03,IF(LEFT(B29,5)="Extra",0.05,"n/a"))))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B29" s="35"/>
+        <v>0.01</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>39</v>
+      </c>
       <c r="C29" s="37" t="s">
         <v>33</v>
       </c>
@@ -2868,17 +3736,21 @@
     </row>
     <row r="35" spans="1:5" ht="15.9" thickBot="1"/>
     <row r="36" spans="1:5" ht="36.9" thickBot="1">
-      <c r="A36" s="34" t="str">
+      <c r="A36" s="34">
         <f>IF(LEFT(B36,5)="Small",0.01,IF(LEFT(B36,3)="Big",0.03,IF(LEFT(B36,4)="Lots",0.05,"n/a")))</f>
-        <v>n/a</v>
-      </c>
-      <c r="B36" s="35"/>
+        <v>0.01</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="C36" s="36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="64.150000000000006" customHeight="1" thickBot="1">
-      <c r="A37" s="45"/>
+      <c r="A37" s="45" t="s">
+        <v>41</v>
+      </c>
       <c r="B37" s="46"/>
       <c r="C37" s="47"/>
       <c r="E37" s="1"/>
@@ -2933,73 +3805,73 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B9">
-    <cfRule type="beginsWith" dxfId="70" priority="89" stopIfTrue="1" operator="beginsWith" text="No Progress">
+    <cfRule type="beginsWith" dxfId="70" priority="85" stopIfTrue="1" operator="beginsWith" text="No Credit">
+      <formula>LEFT(B6,LEN("No Credit"))="No Credit"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="69" priority="86" stopIfTrue="1" operator="beginsWith" text="Not">
+      <formula>LEFT(B6,LEN("Not"))="Not"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="68" priority="87" stopIfTrue="1" operator="endsWith" text="Missed">
+      <formula>RIGHT(B6,LEN("Missed"))="Missed"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="67" priority="88" stopIfTrue="1" operator="beginsWith" text="Partial">
+      <formula>LEFT(B6,LEN("Partial"))="Partial"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="66" priority="89" stopIfTrue="1" operator="beginsWith" text="No Progress">
       <formula>LEFT(B6,LEN("No Progress"))="No Progress"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="69" priority="98" stopIfTrue="1" operator="beginsWith" text="Lots">
+    <cfRule type="beginsWith" dxfId="65" priority="90" stopIfTrue="1" operator="beginsWith" text="Small">
+      <formula>LEFT(B6,LEN("Small"))="Small"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="64" priority="91" stopIfTrue="1" operator="beginsWith" text="Some">
+      <formula>LEFT(B6,LEN("Some"))="Some"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="63" priority="92" stopIfTrue="1" operator="beginsWith" text="Full">
+      <formula>LEFT(B6,LEN("Full"))="Full"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="62" priority="93" stopIfTrue="1" operator="beginsWith" text="Big">
+      <formula>LEFT(B6,LEN("Big"))="Big"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="61" priority="94" stopIfTrue="1" operator="endsWith" text="Met">
+      <formula>RIGHT(B6,LEN("Met"))="Met"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="60" priority="98" stopIfTrue="1" operator="beginsWith" text="Lots">
       <formula>LEFT(B6,LEN("Lots"))="Lots"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="68" priority="94" stopIfTrue="1" operator="endsWith" text="Met">
-      <formula>RIGHT(B6,LEN("Met"))="Met"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="67" priority="93" stopIfTrue="1" operator="beginsWith" text="Big">
-      <formula>LEFT(B6,LEN("Big"))="Big"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="66" priority="92" stopIfTrue="1" operator="beginsWith" text="Full">
-      <formula>LEFT(B6,LEN("Full"))="Full"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="65" priority="91" stopIfTrue="1" operator="beginsWith" text="Some">
-      <formula>LEFT(B6,LEN("Some"))="Some"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="64" priority="90" stopIfTrue="1" operator="beginsWith" text="Small">
-      <formula>LEFT(B6,LEN("Small"))="Small"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="63" priority="88" stopIfTrue="1" operator="beginsWith" text="Partial">
-      <formula>LEFT(B6,LEN("Partial"))="Partial"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="62" priority="87" stopIfTrue="1" operator="endsWith" text="Missed">
-      <formula>RIGHT(B6,LEN("Missed"))="Missed"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="61" priority="86" stopIfTrue="1" operator="beginsWith" text="Not">
-      <formula>LEFT(B6,LEN("Not"))="Not"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="60" priority="85" stopIfTrue="1" operator="beginsWith" text="No Credit">
-      <formula>LEFT(B6,LEN("No Credit"))="No Credit"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:B14 B26:B29">
-    <cfRule type="beginsWith" dxfId="59" priority="83" stopIfTrue="1" operator="beginsWith" text="Extra">
+    <cfRule type="beginsWith" dxfId="59" priority="73" stopIfTrue="1" operator="beginsWith" text="No Credit">
+      <formula>LEFT(B11,LEN("No Credit"))="No Credit"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="58" priority="74" stopIfTrue="1" operator="beginsWith" text="Not">
+      <formula>LEFT(B11,LEN("Not"))="Not"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="57" priority="75" stopIfTrue="1" operator="endsWith" text="Missed">
+      <formula>RIGHT(B11,LEN("Missed"))="Missed"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="56" priority="76" stopIfTrue="1" operator="beginsWith" text="Partial">
+      <formula>LEFT(B11,LEN("Partial"))="Partial"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="55" priority="77" stopIfTrue="1" operator="beginsWith" text="No Progress">
+      <formula>LEFT(B11,LEN("No Progress"))="No Progress"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="54" priority="78" stopIfTrue="1" operator="beginsWith" text="Small">
+      <formula>LEFT(B11,LEN("Small"))="Small"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="53" priority="79" stopIfTrue="1" operator="beginsWith" text="Some">
+      <formula>LEFT(B11,LEN("Some"))="Some"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="52" priority="80" stopIfTrue="1" operator="beginsWith" text="Full">
+      <formula>LEFT(B11,LEN("Full"))="Full"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="51" priority="81" stopIfTrue="1" operator="beginsWith" text="Big">
+      <formula>LEFT(B11,LEN("Big"))="Big"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="50" priority="82" stopIfTrue="1" operator="endsWith" text="Met">
+      <formula>RIGHT(B11,LEN("Met"))="Met"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="49" priority="83" stopIfTrue="1" operator="beginsWith" text="Extra">
       <formula>LEFT(B11,LEN("Extra"))="Extra"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="58" priority="82" stopIfTrue="1" operator="endsWith" text="Met">
-      <formula>RIGHT(B11,LEN("Met"))="Met"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="57" priority="81" stopIfTrue="1" operator="beginsWith" text="Big">
-      <formula>LEFT(B11,LEN("Big"))="Big"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="56" priority="79" stopIfTrue="1" operator="beginsWith" text="Some">
-      <formula>LEFT(B11,LEN("Some"))="Some"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="55" priority="78" stopIfTrue="1" operator="beginsWith" text="Small">
-      <formula>LEFT(B11,LEN("Small"))="Small"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="54" priority="77" stopIfTrue="1" operator="beginsWith" text="No Progress">
-      <formula>LEFT(B11,LEN("No Progress"))="No Progress"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="53" priority="76" stopIfTrue="1" operator="beginsWith" text="Partial">
-      <formula>LEFT(B11,LEN("Partial"))="Partial"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="52" priority="75" stopIfTrue="1" operator="endsWith" text="Missed">
-      <formula>RIGHT(B11,LEN("Missed"))="Missed"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="51" priority="74" stopIfTrue="1" operator="beginsWith" text="Not">
-      <formula>LEFT(B11,LEN("Not"))="Not"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="50" priority="73" stopIfTrue="1" operator="beginsWith" text="No Credit">
-      <formula>LEFT(B11,LEN("No Credit"))="No Credit"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="49" priority="80" stopIfTrue="1" operator="beginsWith" text="Full">
-      <formula>LEFT(B11,LEN("Full"))="Full"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="48" priority="84" stopIfTrue="1" operator="beginsWith" text="Lots">
       <formula>LEFT(B11,LEN("Lots"))="Lots"</formula>
@@ -3033,128 +3905,128 @@
     <cfRule type="beginsWith" dxfId="39" priority="9" stopIfTrue="1" operator="beginsWith" text="Big">
       <formula>LEFT(B16,LEN("Big"))="Big"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="38" priority="11" stopIfTrue="1" operator="beginsWith" text="Extra">
+    <cfRule type="endsWith" dxfId="38" priority="10" stopIfTrue="1" operator="endsWith" text="Met">
+      <formula>RIGHT(B16,LEN("Met"))="Met"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="37" priority="11" stopIfTrue="1" operator="beginsWith" text="Extra">
       <formula>LEFT(B16,LEN("Extra"))="Extra"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="37" priority="12" stopIfTrue="1" operator="beginsWith" text="Lots">
+    <cfRule type="beginsWith" dxfId="36" priority="12" stopIfTrue="1" operator="beginsWith" text="Lots">
       <formula>LEFT(B16,LEN("Lots"))="Lots"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="36" priority="10" stopIfTrue="1" operator="endsWith" text="Met">
-      <formula>RIGHT(B16,LEN("Met"))="Met"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:B24">
-    <cfRule type="endsWith" dxfId="35" priority="51" stopIfTrue="1" operator="endsWith" text="Missed">
+    <cfRule type="beginsWith" dxfId="35" priority="49" stopIfTrue="1" operator="beginsWith" text="No Credit">
+      <formula>LEFT(B21,LEN("No Credit"))="No Credit"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="34" priority="50" stopIfTrue="1" operator="beginsWith" text="Not">
+      <formula>LEFT(B21,LEN("Not"))="Not"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="33" priority="51" stopIfTrue="1" operator="endsWith" text="Missed">
       <formula>RIGHT(B21,LEN("Missed"))="Missed"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="34" priority="52" stopIfTrue="1" operator="beginsWith" text="Partial">
+    <cfRule type="beginsWith" dxfId="32" priority="52" stopIfTrue="1" operator="beginsWith" text="Partial">
       <formula>LEFT(B21,LEN("Partial"))="Partial"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="33" priority="53" stopIfTrue="1" operator="beginsWith" text="No Progress">
+    <cfRule type="beginsWith" dxfId="31" priority="53" stopIfTrue="1" operator="beginsWith" text="No Progress">
       <formula>LEFT(B21,LEN("No Progress"))="No Progress"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="32" priority="54" stopIfTrue="1" operator="beginsWith" text="Small">
+    <cfRule type="beginsWith" dxfId="30" priority="54" stopIfTrue="1" operator="beginsWith" text="Small">
       <formula>LEFT(B21,LEN("Small"))="Small"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="31" priority="55" stopIfTrue="1" operator="beginsWith" text="Some">
+    <cfRule type="beginsWith" dxfId="29" priority="55" stopIfTrue="1" operator="beginsWith" text="Some">
       <formula>LEFT(B21,LEN("Some"))="Some"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="30" priority="56" stopIfTrue="1" operator="beginsWith" text="Full">
+    <cfRule type="beginsWith" dxfId="28" priority="56" stopIfTrue="1" operator="beginsWith" text="Full">
       <formula>LEFT(B21,LEN("Full"))="Full"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="29" priority="57" stopIfTrue="1" operator="beginsWith" text="Big">
+    <cfRule type="beginsWith" dxfId="27" priority="57" stopIfTrue="1" operator="beginsWith" text="Big">
       <formula>LEFT(B21,LEN("Big"))="Big"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="28" priority="58" stopIfTrue="1" operator="endsWith" text="Met">
+    <cfRule type="endsWith" dxfId="26" priority="58" stopIfTrue="1" operator="endsWith" text="Met">
       <formula>RIGHT(B21,LEN("Met"))="Met"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="27" priority="50" stopIfTrue="1" operator="beginsWith" text="Not">
-      <formula>LEFT(B21,LEN("Not"))="Not"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="26" priority="60" stopIfTrue="1" operator="beginsWith" text="Lots">
+    <cfRule type="beginsWith" dxfId="25" priority="59" stopIfTrue="1" operator="beginsWith" text="Extra">
+      <formula>LEFT(B21,LEN("Extra"))="Extra"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="24" priority="60" stopIfTrue="1" operator="beginsWith" text="Lots">
       <formula>LEFT(B21,LEN("Lots"))="Lots"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="25" priority="49" stopIfTrue="1" operator="beginsWith" text="No Credit">
-      <formula>LEFT(B21,LEN("No Credit"))="No Credit"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="24" priority="59" stopIfTrue="1" operator="beginsWith" text="Extra">
-      <formula>LEFT(B21,LEN("Extra"))="Extra"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:B34">
-    <cfRule type="beginsWith" dxfId="23" priority="29" stopIfTrue="1" operator="beginsWith" text="No Progress">
+    <cfRule type="beginsWith" dxfId="23" priority="25" stopIfTrue="1" operator="beginsWith" text="No Credit">
+      <formula>LEFT(B31,LEN("No Credit"))="No Credit"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="22" priority="26" stopIfTrue="1" operator="beginsWith" text="Not">
+      <formula>LEFT(B31,LEN("Not"))="Not"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="21" priority="27" stopIfTrue="1" operator="endsWith" text="Missed">
+      <formula>RIGHT(B31,LEN("Missed"))="Missed"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="20" priority="28" stopIfTrue="1" operator="beginsWith" text="Partial">
+      <formula>LEFT(B31,LEN("Partial"))="Partial"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="19" priority="29" stopIfTrue="1" operator="beginsWith" text="No Progress">
       <formula>LEFT(B31,LEN("No Progress"))="No Progress"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="22" priority="36" stopIfTrue="1" operator="beginsWith" text="Lots">
-      <formula>LEFT(B31,LEN("Lots"))="Lots"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="21" priority="35" stopIfTrue="1" operator="beginsWith" text="Extra">
-      <formula>LEFT(B31,LEN("Extra"))="Extra"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="20" priority="34" stopIfTrue="1" operator="endsWith" text="Met">
-      <formula>RIGHT(B31,LEN("Met"))="Met"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="19" priority="33" stopIfTrue="1" operator="beginsWith" text="Big">
-      <formula>LEFT(B31,LEN("Big"))="Big"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="18" priority="32" stopIfTrue="1" operator="beginsWith" text="Full">
-      <formula>LEFT(B31,LEN("Full"))="Full"</formula>
+    <cfRule type="beginsWith" dxfId="18" priority="30" stopIfTrue="1" operator="beginsWith" text="Small">
+      <formula>LEFT(B31,LEN("Small"))="Small"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="17" priority="31" stopIfTrue="1" operator="beginsWith" text="Some">
       <formula>LEFT(B31,LEN("Some"))="Some"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="16" priority="30" stopIfTrue="1" operator="beginsWith" text="Small">
-      <formula>LEFT(B31,LEN("Small"))="Small"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="15" priority="27" stopIfTrue="1" operator="endsWith" text="Missed">
-      <formula>RIGHT(B31,LEN("Missed"))="Missed"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="14" priority="26" stopIfTrue="1" operator="beginsWith" text="Not">
-      <formula>LEFT(B31,LEN("Not"))="Not"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="13" priority="25" stopIfTrue="1" operator="beginsWith" text="No Credit">
-      <formula>LEFT(B31,LEN("No Credit"))="No Credit"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="12" priority="28" stopIfTrue="1" operator="beginsWith" text="Partial">
-      <formula>LEFT(B31,LEN("Partial"))="Partial"</formula>
+    <cfRule type="beginsWith" dxfId="16" priority="32" stopIfTrue="1" operator="beginsWith" text="Full">
+      <formula>LEFT(B31,LEN("Full"))="Full"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="15" priority="33" stopIfTrue="1" operator="beginsWith" text="Big">
+      <formula>LEFT(B31,LEN("Big"))="Big"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="14" priority="34" stopIfTrue="1" operator="endsWith" text="Met">
+      <formula>RIGHT(B31,LEN("Met"))="Met"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="13" priority="35" stopIfTrue="1" operator="beginsWith" text="Extra">
+      <formula>LEFT(B31,LEN("Extra"))="Extra"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="12" priority="36" stopIfTrue="1" operator="beginsWith" text="Lots">
+      <formula>LEFT(B31,LEN("Lots"))="Lots"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="beginsWith" dxfId="11" priority="24" stopIfTrue="1" operator="beginsWith" text="Lots">
+    <cfRule type="beginsWith" dxfId="11" priority="13" stopIfTrue="1" operator="beginsWith" text="No Credit">
+      <formula>LEFT(B36,LEN("No Credit"))="No Credit"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="10" priority="14" stopIfTrue="1" operator="beginsWith" text="Not">
+      <formula>LEFT(B36,LEN("Not"))="Not"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="9" priority="15" stopIfTrue="1" operator="endsWith" text="Missed">
+      <formula>RIGHT(B36,LEN("Missed"))="Missed"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="8" priority="16" stopIfTrue="1" operator="beginsWith" text="Partial">
+      <formula>LEFT(B36,LEN("Partial"))="Partial"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="7" priority="17" stopIfTrue="1" operator="beginsWith" text="No Progress">
+      <formula>LEFT(B36,LEN("No Progress"))="No Progress"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="6" priority="18" stopIfTrue="1" operator="beginsWith" text="Small">
+      <formula>LEFT(B36,LEN("Small"))="Small"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="5" priority="19" stopIfTrue="1" operator="beginsWith" text="Some">
+      <formula>LEFT(B36,LEN("Some"))="Some"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="4" priority="20" stopIfTrue="1" operator="beginsWith" text="Full">
+      <formula>LEFT(B36,LEN("Full"))="Full"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="3" priority="21" stopIfTrue="1" operator="beginsWith" text="Big">
+      <formula>LEFT(B36,LEN("Big"))="Big"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="2" priority="22" stopIfTrue="1" operator="endsWith" text="Met">
+      <formula>RIGHT(B36,LEN("Met"))="Met"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="1" priority="23" stopIfTrue="1" operator="beginsWith" text="Extra">
+      <formula>LEFT(B36,LEN("Extra"))="Extra"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="0" priority="24" stopIfTrue="1" operator="beginsWith" text="Lots">
       <formula>LEFT(B36,LEN("Lots"))="Lots"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="10" priority="23" stopIfTrue="1" operator="beginsWith" text="Extra">
-      <formula>LEFT(B36,LEN("Extra"))="Extra"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="9" priority="22" stopIfTrue="1" operator="endsWith" text="Met">
-      <formula>RIGHT(B36,LEN("Met"))="Met"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="8" priority="21" stopIfTrue="1" operator="beginsWith" text="Big">
-      <formula>LEFT(B36,LEN("Big"))="Big"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="7" priority="20" stopIfTrue="1" operator="beginsWith" text="Full">
-      <formula>LEFT(B36,LEN("Full"))="Full"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="6" priority="19" stopIfTrue="1" operator="beginsWith" text="Some">
-      <formula>LEFT(B36,LEN("Some"))="Some"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="5" priority="18" stopIfTrue="1" operator="beginsWith" text="Small">
-      <formula>LEFT(B36,LEN("Small"))="Small"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="4" priority="17" stopIfTrue="1" operator="beginsWith" text="No Progress">
-      <formula>LEFT(B36,LEN("No Progress"))="No Progress"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="3" priority="16" stopIfTrue="1" operator="beginsWith" text="Partial">
-      <formula>LEFT(B36,LEN("Partial"))="Partial"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="2" priority="15" stopIfTrue="1" operator="endsWith" text="Missed">
-      <formula>RIGHT(B36,LEN("Missed"))="Missed"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="1" priority="14" stopIfTrue="1" operator="beginsWith" text="Not">
-      <formula>LEFT(B36,LEN("Not"))="Not"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="0" priority="13" stopIfTrue="1" operator="beginsWith" text="No Credit">
-      <formula>LEFT(B36,LEN("No Credit"))="No Credit"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
@@ -3180,7 +4052,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9B2E6A-0D51-4D50-A1BC-AE4071052ED9}">
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="89.68359375" customWidth="1"/>
@@ -3194,11 +4066,13 @@
     <row r="2" spans="1:1" s="7" customFormat="1" ht="15.9" thickBot="1">
       <c r="A2" s="8" t="str">
         <f>IF(LEN(A3) &gt; 2000,"-----",IF(LEN(A3) &gt; 1000,"---",IF(LEN(A3) &gt; 500,"You need more post-mortem reflection.",IF(A3&gt;0,"You need A LOT MORE post-mortem reflection.","How did the project go? What did you learn? What could you improve?"))))</f>
-        <v>How did the project go? What did you learn? What could you improve?</v>
+        <v>---</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="409.5" customHeight="1">
-      <c r="A3" s="48"/>
+      <c r="A3" s="48" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="49"/>
@@ -3340,6 +4214,11 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="49"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3417,7 +4296,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE6F06A3-3058-4E5E-8648-85AEA2F13214}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr defaultColWidth="9.05078125" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="172.7890625" style="29" customWidth="1"/>
@@ -3434,8 +4313,83 @@
         <v>4</v>
       </c>
     </row>
+    <row r="3" spans="1:1" ht="30" customHeight="1">
+      <c r="A3" s="29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="19.5" customHeight="1">
+      <c r="A4" s="29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="409" customHeight="1">
+      <c r="A5" s="52" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="409.5">
+      <c r="A7" s="52" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="409.5">
+      <c r="A9" s="52" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="172.8">
+      <c r="A11" s="52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="409.5">
+      <c r="A14" s="52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="409.5">
+      <c r="A16" s="52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="409.5">
+      <c r="A18" s="52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="409.5">
+      <c r="A20" s="52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="409.5">
+      <c r="A23" s="52" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="409.5">
+      <c r="A26" s="52" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="409.5">
+      <c r="A28" s="52" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3" xr:uid="{BDA3E28D-9CA2-4C11-BA20-5C2D734C54D6}">
       <formula1>"Lab A Goals Met,Lab B Goals Met,Lab C Goals Met,Lab D Goals Met, Lab E Goals Met"</formula1>
     </dataValidation>
